--- a/tasks.xlsx
+++ b/tasks.xlsx
@@ -16,9 +16,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
+  <numFmts count="4">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
+    <numFmt numFmtId="166" formatCode="yyyy-mm-dd"/>
+    <numFmt numFmtId="167" formatCode="YYYY-MM-DD"/>
   </numFmts>
   <fonts count="2">
     <font>
@@ -58,12 +60,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -429,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L4"/>
+  <dimension ref="A1:L6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -580,7 +583,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Completed</t>
+          <t>In Progress</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -589,13 +592,14 @@
         </is>
       </c>
       <c r="I3" s="2" t="n">
-        <v>46117.51312829911</v>
+        <v>46117.60639489583</v>
       </c>
       <c r="J3" t="inlineStr">
         <is>
           <t xml:space="preserve">nan
 [2026-04-05 12:18] 
-[2026-04-05 12:18] </t>
+[2026-04-05 12:18] 
+[2026-04-05 14:33] </t>
         </is>
       </c>
       <c r="K3" t="n">
@@ -661,6 +665,82 @@
           <t>Testing</t>
         </is>
       </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>75e13cbb-8fea-40f3-865e-32f39c2e73ee</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>dmeo</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr"/>
+      <c r="D5" t="inlineStr"/>
+      <c r="E5" s="2" t="n">
+        <v>46117.60648322917</v>
+      </c>
+      <c r="F5" s="2" t="n">
+        <v>46117</v>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="n">
+        <v>46117.60648322917</v>
+      </c>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>424780b3-e68e-4462-8e62-6f1014a9f33d</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>nkdsclavnk</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr"/>
+      <c r="D6" t="inlineStr"/>
+      <c r="E6" s="2" t="n">
+        <v>46117.60674136408</v>
+      </c>
+      <c r="F6" s="3" t="n">
+        <v>46114</v>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="n">
+        <v>46117.60674136411</v>
+      </c>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="n">
+        <v>0</v>
+      </c>
+      <c r="L6" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
